--- a/main/academic_time_table.xlsx
+++ b/main/academic_time_table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ronak_8q45q08\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d4ed0cf1bf3432fc/Desktop/srm attendance calculator/calc_attendence/main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98261F3F-E8D5-4493-B967-ED1E4C450DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{98261F3F-E8D5-4493-B967-ED1E4C450DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E7EB99F-D642-42EB-8E0A-67F4094372D8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A757884B-7843-4405-99AB-51A9CEB2882C}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{A757884B-7843-4405-99AB-51A9CEB2882C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/main/academic_time_table.xlsx
+++ b/main/academic_time_table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d4ed0cf1bf3432fc/Desktop/srm attendance calculator/calc_attendence/main/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ronak_8q45q08\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{98261F3F-E8D5-4493-B967-ED1E4C450DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E7EB99F-D642-42EB-8E0A-67F4094372D8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{98261F3F-E8D5-4493-B967-ED1E4C450DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{A757884B-7843-4405-99AB-51A9CEB2882C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A757884B-7843-4405-99AB-51A9CEB2882C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/main/academic_time_table.xlsx
+++ b/main/academic_time_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ronak_8q45q08\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ronak_8q45q08\Desktop\Ronak\srm attendance calculator\calc_attendence\main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98261F3F-E8D5-4493-B967-ED1E4C450DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2D7BDB-6000-4AB0-AFAD-2F48D54AE90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A757884B-7843-4405-99AB-51A9CEB2882C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{A757884B-7843-4405-99AB-51A9CEB2882C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -827,6 +827,9 @@
       <c r="L4">
         <v>1</v>
       </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
@@ -851,7 +854,9 @@
         <v>1</v>
       </c>
       <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
       <c r="J5" s="2">
         <v>1</v>
       </c>
@@ -919,9 +924,6 @@
       <c r="K8">
         <v>2</v>
       </c>
-      <c r="M8">
-        <v>2</v>
-      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
@@ -939,6 +941,7 @@
       <c r="E9" s="13" t="s">
         <v>16</v>
       </c>
+      <c r="F9" s="6"/>
       <c r="L9">
         <v>2</v>
       </c>
@@ -959,7 +962,7 @@
       <c r="E10" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="2"/>
+      <c r="F10" s="7"/>
       <c r="G10" s="2">
         <v>2</v>
       </c>
@@ -988,7 +991,7 @@
       <c r="E11" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="8">
         <v>1</v>
       </c>
       <c r="G11" s="2">
@@ -1001,6 +1004,9 @@
       <c r="J11" s="2"/>
       <c r="L11">
         <v>1</v>
+      </c>
+      <c r="M11">
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -1026,7 +1032,9 @@
         <v>1</v>
       </c>
       <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
       <c r="J12" s="2">
         <v>1</v>
       </c>
@@ -1093,9 +1101,6 @@
       <c r="K15">
         <v>2</v>
       </c>
-      <c r="M15">
-        <v>2</v>
-      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
@@ -1113,6 +1118,7 @@
       <c r="E16" s="13" t="s">
         <v>16</v>
       </c>
+      <c r="F16" s="6"/>
       <c r="L16">
         <v>2</v>
       </c>
@@ -1133,7 +1139,7 @@
       <c r="E17" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F17" s="2"/>
+      <c r="F17" s="7"/>
       <c r="G17" s="2">
         <v>2</v>
       </c>
@@ -1162,7 +1168,7 @@
       <c r="E18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="8">
         <v>1</v>
       </c>
       <c r="G18" s="2">
@@ -1175,6 +1181,9 @@
       <c r="J18" s="2"/>
       <c r="L18">
         <v>1</v>
+      </c>
+      <c r="M18">
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
@@ -1200,7 +1209,9 @@
         <v>1</v>
       </c>
       <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
+      <c r="I19" s="2">
+        <v>1</v>
+      </c>
       <c r="J19" s="2">
         <v>1</v>
       </c>
@@ -1267,9 +1278,6 @@
       <c r="K22">
         <v>2</v>
       </c>
-      <c r="M22">
-        <v>2</v>
-      </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
@@ -1287,6 +1295,7 @@
       <c r="E23" s="13" t="s">
         <v>16</v>
       </c>
+      <c r="F23" s="6"/>
       <c r="L23">
         <v>2</v>
       </c>
@@ -1307,7 +1316,7 @@
       <c r="E24" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F24" s="2"/>
+      <c r="F24" s="7"/>
       <c r="G24" s="2">
         <v>2</v>
       </c>
@@ -1336,7 +1345,7 @@
       <c r="E25" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="8">
         <v>1</v>
       </c>
       <c r="G25" s="2">
@@ -1349,6 +1358,9 @@
       <c r="J25" s="2"/>
       <c r="L25">
         <v>1</v>
+      </c>
+      <c r="M25">
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
@@ -1374,7 +1386,9 @@
         <v>1</v>
       </c>
       <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
+      <c r="I26" s="2">
+        <v>1</v>
+      </c>
       <c r="J26" s="2">
         <v>1</v>
       </c>
@@ -1441,9 +1455,6 @@
       <c r="K29">
         <v>2</v>
       </c>
-      <c r="M29">
-        <v>2</v>
-      </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
@@ -1461,6 +1472,7 @@
       <c r="E30" s="13" t="s">
         <v>16</v>
       </c>
+      <c r="F30" s="6"/>
       <c r="L30">
         <v>2</v>
       </c>
@@ -1481,7 +1493,7 @@
       <c r="E31" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F31" s="2"/>
+      <c r="F31" s="7"/>
       <c r="G31" s="2">
         <v>2</v>
       </c>
@@ -1510,7 +1522,7 @@
       <c r="E32" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="8">
         <v>1</v>
       </c>
       <c r="G32" s="2">
@@ -1523,6 +1535,9 @@
       <c r="J32" s="2"/>
       <c r="L32">
         <v>1</v>
+      </c>
+      <c r="M32">
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -1548,7 +1563,9 @@
         <v>1</v>
       </c>
       <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
+      <c r="I33" s="2">
+        <v>1</v>
+      </c>
       <c r="J33" s="2">
         <v>1</v>
       </c>
@@ -1615,9 +1632,6 @@
       <c r="K36">
         <v>2</v>
       </c>
-      <c r="M36">
-        <v>2</v>
-      </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="9">
@@ -1715,6 +1729,9 @@
       <c r="L40">
         <v>1</v>
       </c>
+      <c r="M40">
+        <v>2</v>
+      </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="9">
@@ -1773,7 +1790,9 @@
         <v>1</v>
       </c>
       <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
+      <c r="I43" s="2">
+        <v>1</v>
+      </c>
       <c r="J43" s="2">
         <v>1</v>
       </c>
@@ -1806,9 +1825,6 @@
       <c r="K44">
         <v>2</v>
       </c>
-      <c r="M44">
-        <v>2</v>
-      </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="9">
@@ -1940,6 +1956,9 @@
       <c r="L50">
         <v>1</v>
       </c>
+      <c r="M50">
+        <v>2</v>
+      </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="9">
@@ -1964,7 +1983,9 @@
         <v>1</v>
       </c>
       <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
+      <c r="I51" s="2">
+        <v>1</v>
+      </c>
       <c r="J51" s="2">
         <v>1</v>
       </c>
@@ -1997,9 +2018,6 @@
       <c r="K52">
         <v>2</v>
       </c>
-      <c r="M52">
-        <v>2</v>
-      </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="9">
@@ -2131,6 +2149,9 @@
       <c r="L58">
         <v>1</v>
       </c>
+      <c r="M58">
+        <v>2</v>
+      </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="9">
@@ -2155,7 +2176,9 @@
         <v>1</v>
       </c>
       <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
+      <c r="I59" s="2">
+        <v>1</v>
+      </c>
       <c r="J59" s="2">
         <v>1</v>
       </c>
@@ -2188,9 +2211,6 @@
       <c r="K60">
         <v>2</v>
       </c>
-      <c r="M60">
-        <v>2</v>
-      </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="9">
@@ -2305,6 +2325,9 @@
       <c r="L65">
         <v>1</v>
       </c>
+      <c r="M65">
+        <v>2</v>
+      </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
@@ -2329,7 +2352,9 @@
         <v>1</v>
       </c>
       <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
+      <c r="I66" s="2">
+        <v>1</v>
+      </c>
       <c r="J66" s="2">
         <v>1</v>
       </c>
@@ -2362,9 +2387,6 @@
       <c r="K67">
         <v>2</v>
       </c>
-      <c r="M67">
-        <v>2</v>
-      </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
@@ -2479,6 +2501,9 @@
       <c r="L72">
         <v>1</v>
       </c>
+      <c r="M72">
+        <v>2</v>
+      </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="9">
@@ -2503,7 +2528,9 @@
         <v>1</v>
       </c>
       <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
+      <c r="I73" s="2">
+        <v>1</v>
+      </c>
       <c r="J73" s="2">
         <v>1</v>
       </c>
@@ -2536,9 +2563,6 @@
       <c r="K74">
         <v>2</v>
       </c>
-      <c r="M74">
-        <v>2</v>
-      </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="9">
@@ -2639,6 +2663,9 @@
       <c r="L79">
         <v>1</v>
       </c>
+      <c r="M79">
+        <v>2</v>
+      </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="9">
@@ -2694,7 +2721,9 @@
         <v>1</v>
       </c>
       <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
+      <c r="I81" s="2">
+        <v>1</v>
+      </c>
       <c r="J81" s="2">
         <v>1</v>
       </c>
@@ -2727,9 +2756,6 @@
       <c r="K82">
         <v>2</v>
       </c>
-      <c r="M82">
-        <v>2</v>
-      </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="9">
@@ -2844,6 +2870,9 @@
       <c r="L87">
         <v>1</v>
       </c>
+      <c r="M87">
+        <v>2</v>
+      </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="9">
@@ -2868,7 +2897,9 @@
         <v>1</v>
       </c>
       <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
+      <c r="I88" s="2">
+        <v>1</v>
+      </c>
       <c r="J88" s="2">
         <v>1</v>
       </c>
@@ -2901,9 +2932,6 @@
       <c r="K89">
         <v>2</v>
       </c>
-      <c r="M89">
-        <v>2</v>
-      </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="9">
@@ -3052,6 +3080,9 @@
       <c r="L96">
         <v>1</v>
       </c>
+      <c r="M96">
+        <v>2</v>
+      </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="9">
@@ -3110,7 +3141,9 @@
         <v>1</v>
       </c>
       <c r="H99" s="2"/>
-      <c r="I99" s="2"/>
+      <c r="I99" s="2">
+        <v>1</v>
+      </c>
       <c r="J99" s="2">
         <v>1</v>
       </c>
@@ -3143,9 +3176,6 @@
       <c r="K100">
         <v>2</v>
       </c>
-      <c r="M100">
-        <v>2</v>
-      </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="9">
@@ -3226,6 +3256,9 @@
       <c r="L103">
         <v>1</v>
       </c>
+      <c r="M103">
+        <v>2</v>
+      </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="9">
@@ -3284,7 +3317,9 @@
         <v>1</v>
       </c>
       <c r="H106" s="2"/>
-      <c r="I106" s="2"/>
+      <c r="I106" s="2">
+        <v>1</v>
+      </c>
       <c r="J106" s="2">
         <v>1</v>
       </c>
@@ -3317,9 +3352,6 @@
       <c r="K107">
         <v>2</v>
       </c>
-      <c r="M107">
-        <v>2</v>
-      </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="9">
@@ -3400,6 +3432,9 @@
       <c r="L110">
         <v>1</v>
       </c>
+      <c r="M110">
+        <v>2</v>
+      </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="9">
@@ -3458,7 +3493,9 @@
         <v>1</v>
       </c>
       <c r="H113" s="2"/>
-      <c r="I113" s="2"/>
+      <c r="I113" s="2">
+        <v>1</v>
+      </c>
       <c r="J113" s="2">
         <v>1</v>
       </c>
@@ -3491,9 +3528,6 @@
       <c r="K114">
         <v>2</v>
       </c>
-      <c r="M114">
-        <v>2</v>
-      </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="9">
@@ -3574,6 +3608,9 @@
       <c r="L117">
         <v>1</v>
       </c>
+      <c r="M117">
+        <v>2</v>
+      </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="9">
@@ -3632,7 +3669,9 @@
         <v>1</v>
       </c>
       <c r="H120" s="2"/>
-      <c r="I120" s="2"/>
+      <c r="I120" s="2">
+        <v>1</v>
+      </c>
       <c r="J120" s="2">
         <v>1</v>
       </c>
@@ -3665,9 +3704,6 @@
       <c r="K121">
         <v>2</v>
       </c>
-      <c r="M121">
-        <v>2</v>
-      </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="9">
@@ -3748,6 +3784,9 @@
       <c r="L124">
         <v>1</v>
       </c>
+      <c r="M124">
+        <v>2</v>
+      </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="9">
@@ -3806,7 +3845,9 @@
         <v>1</v>
       </c>
       <c r="H127" s="2"/>
-      <c r="I127" s="2"/>
+      <c r="I127" s="2">
+        <v>1</v>
+      </c>
       <c r="J127" s="2">
         <v>1</v>
       </c>
@@ -3839,9 +3880,6 @@
       <c r="K128">
         <v>2</v>
       </c>
-      <c r="M128">
-        <v>2</v>
-      </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="9">
@@ -3922,6 +3960,9 @@
       <c r="L131">
         <v>1</v>
       </c>
+      <c r="M131">
+        <v>2</v>
+      </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="9">
@@ -3980,7 +4021,9 @@
         <v>1</v>
       </c>
       <c r="H134" s="2"/>
-      <c r="I134" s="2"/>
+      <c r="I134" s="2">
+        <v>1</v>
+      </c>
       <c r="J134" s="2">
         <v>1</v>
       </c>
@@ -4013,9 +4056,6 @@
       <c r="K135">
         <v>2</v>
       </c>
-      <c r="M135">
-        <v>2</v>
-      </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" s="9">
@@ -4096,6 +4136,9 @@
       <c r="L138">
         <v>1</v>
       </c>
+      <c r="M138">
+        <v>2</v>
+      </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="9">
@@ -4154,7 +4197,9 @@
         <v>1</v>
       </c>
       <c r="H141" s="2"/>
-      <c r="I141" s="2"/>
+      <c r="I141" s="2">
+        <v>1</v>
+      </c>
       <c r="J141" s="2">
         <v>1</v>
       </c>

--- a/main/academic_time_table.xlsx
+++ b/main/academic_time_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ronak_8q45q08\Desktop\Ronak\srm attendance calculator\calc_attendence\main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2D7BDB-6000-4AB0-AFAD-2F48D54AE90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74EEE1E8-CA55-4E33-8D01-6FB3B324062B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{A757884B-7843-4405-99AB-51A9CEB2882C}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="45">
   <si>
     <t>Holiday</t>
   </si>
@@ -166,15 +166,6 @@
   </si>
   <si>
     <t>Sequence</t>
-  </si>
-  <si>
-    <t>RM(Lab)</t>
-  </si>
-  <si>
-    <t>ML(Lab)</t>
-  </si>
-  <si>
-    <t>ADS(Lab)</t>
   </si>
   <si>
     <t>ML</t>
@@ -692,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{585B69E8-A20C-47AE-8103-368E8ABC7BE0}">
-  <dimension ref="A1:M141"/>
+  <dimension ref="A1:J141"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" style="3" customWidth="1"/>
@@ -701,12 +692,12 @@
     <col min="4" max="4" width="8.88671875" style="3"/>
     <col min="5" max="5" width="9.6640625" style="3" customWidth="1"/>
     <col min="6" max="7" width="8.88671875" style="3"/>
-    <col min="8" max="9" width="10.33203125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" style="3"/>
-    <col min="12" max="12" width="10.6640625" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="3"/>
+    <col min="10" max="10" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>3</v>
       </c>
@@ -726,28 +717,19 @@
         <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="I1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="9">
         <v>46224</v>
       </c>
@@ -764,11 +746,11 @@
         <v>16</v>
       </c>
       <c r="F2" s="6"/>
-      <c r="L2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
         <v>46225</v>
       </c>
@@ -786,18 +768,15 @@
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="2">
-        <v>2</v>
-      </c>
-      <c r="H3" s="2">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H3" s="2"/>
       <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
         <v>46226</v>
       </c>
@@ -819,19 +798,15 @@
       <c r="G4" s="2">
         <v>1</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2">
-        <v>2</v>
-      </c>
-      <c r="J4" s="2"/>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H4" s="2">
+        <v>2</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>46227</v>
       </c>
@@ -853,15 +828,14 @@
       <c r="G5" s="2">
         <v>1</v>
       </c>
-      <c r="H5" s="2"/>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
       <c r="I5" s="2">
         <v>1</v>
       </c>
-      <c r="J5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>46228</v>
       </c>
@@ -879,7 +853,7 @@
       </c>
       <c r="F6" s="2"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>46229</v>
       </c>
@@ -896,7 +870,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>46230</v>
       </c>
@@ -915,17 +889,14 @@
       <c r="F8" s="3">
         <v>1</v>
       </c>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
       <c r="I8" s="3">
-        <v>1</v>
-      </c>
-      <c r="J8" s="3">
-        <v>2</v>
-      </c>
-      <c r="K8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>46231</v>
       </c>
@@ -942,11 +913,11 @@
         <v>16</v>
       </c>
       <c r="F9" s="6"/>
-      <c r="L9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>46232</v>
       </c>
@@ -964,18 +935,15 @@
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="2">
-        <v>2</v>
-      </c>
-      <c r="H10" s="2">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H10" s="2"/>
       <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="L10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>46233</v>
       </c>
@@ -997,19 +965,15 @@
       <c r="G11" s="2">
         <v>1</v>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2">
-        <v>2</v>
-      </c>
-      <c r="J11" s="2"/>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H11" s="2">
+        <v>2</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>46234</v>
       </c>
@@ -1031,15 +995,14 @@
       <c r="G12" s="2">
         <v>1</v>
       </c>
-      <c r="H12" s="2"/>
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
       <c r="I12" s="2">
         <v>1</v>
       </c>
-      <c r="J12" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>46235</v>
       </c>
@@ -1056,7 +1019,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>46236</v>
       </c>
@@ -1073,7 +1036,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>46237</v>
       </c>
@@ -1092,17 +1055,14 @@
       <c r="F15" s="3">
         <v>1</v>
       </c>
+      <c r="H15" s="3">
+        <v>1</v>
+      </c>
       <c r="I15" s="3">
-        <v>1</v>
-      </c>
-      <c r="J15" s="3">
-        <v>2</v>
-      </c>
-      <c r="K15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>46238</v>
       </c>
@@ -1119,11 +1079,11 @@
         <v>16</v>
       </c>
       <c r="F16" s="6"/>
-      <c r="L16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>46239</v>
       </c>
@@ -1141,18 +1101,15 @@
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="2">
-        <v>2</v>
-      </c>
-      <c r="H17" s="2">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H17" s="2"/>
       <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="L17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>46240</v>
       </c>
@@ -1174,19 +1131,15 @@
       <c r="G18" s="2">
         <v>1</v>
       </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2">
-        <v>2</v>
-      </c>
-      <c r="J18" s="2"/>
-      <c r="L18">
-        <v>1</v>
-      </c>
-      <c r="M18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H18" s="2">
+        <v>2</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>46241</v>
       </c>
@@ -1208,15 +1161,14 @@
       <c r="G19" s="2">
         <v>1</v>
       </c>
-      <c r="H19" s="2"/>
+      <c r="H19" s="2">
+        <v>1</v>
+      </c>
       <c r="I19" s="2">
         <v>1</v>
       </c>
-      <c r="J19" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>46242</v>
       </c>
@@ -1233,7 +1185,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>46243</v>
       </c>
@@ -1250,7 +1202,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>46244</v>
       </c>
@@ -1269,17 +1221,14 @@
       <c r="F22" s="3">
         <v>1</v>
       </c>
+      <c r="H22" s="3">
+        <v>1</v>
+      </c>
       <c r="I22" s="3">
-        <v>1</v>
-      </c>
-      <c r="J22" s="3">
-        <v>2</v>
-      </c>
-      <c r="K22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
         <v>46245</v>
       </c>
@@ -1296,11 +1245,11 @@
         <v>16</v>
       </c>
       <c r="F23" s="6"/>
-      <c r="L23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>46246</v>
       </c>
@@ -1318,18 +1267,15 @@
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="2">
-        <v>2</v>
-      </c>
-      <c r="H24" s="2">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H24" s="2"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="L24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
         <v>46247</v>
       </c>
@@ -1351,19 +1297,15 @@
       <c r="G25" s="2">
         <v>1</v>
       </c>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2">
-        <v>2</v>
-      </c>
-      <c r="J25" s="2"/>
-      <c r="L25">
-        <v>1</v>
-      </c>
-      <c r="M25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H25" s="2">
+        <v>2</v>
+      </c>
+      <c r="I25" s="2"/>
+      <c r="J25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>46248</v>
       </c>
@@ -1385,15 +1327,14 @@
       <c r="G26" s="2">
         <v>1</v>
       </c>
-      <c r="H26" s="2"/>
+      <c r="H26" s="2">
+        <v>1</v>
+      </c>
       <c r="I26" s="2">
         <v>1</v>
       </c>
-      <c r="J26" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="9">
         <v>46249</v>
       </c>
@@ -1410,7 +1351,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>46250</v>
       </c>
@@ -1427,7 +1368,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="9">
         <v>46251</v>
       </c>
@@ -1446,17 +1387,14 @@
       <c r="F29" s="3">
         <v>1</v>
       </c>
+      <c r="H29" s="3">
+        <v>1</v>
+      </c>
       <c r="I29" s="3">
-        <v>1</v>
-      </c>
-      <c r="J29" s="3">
-        <v>2</v>
-      </c>
-      <c r="K29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>46252</v>
       </c>
@@ -1473,11 +1411,11 @@
         <v>16</v>
       </c>
       <c r="F30" s="6"/>
-      <c r="L30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="9">
         <v>46253</v>
       </c>
@@ -1495,18 +1433,15 @@
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="2">
-        <v>2</v>
-      </c>
-      <c r="H31" s="2">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H31" s="2"/>
       <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="L31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>46254</v>
       </c>
@@ -1528,19 +1463,15 @@
       <c r="G32" s="2">
         <v>1</v>
       </c>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2">
-        <v>2</v>
-      </c>
-      <c r="J32" s="2"/>
-      <c r="L32">
-        <v>1</v>
-      </c>
-      <c r="M32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H32" s="2">
+        <v>2</v>
+      </c>
+      <c r="I32" s="2"/>
+      <c r="J32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="9">
         <v>46255</v>
       </c>
@@ -1562,15 +1493,14 @@
       <c r="G33" s="2">
         <v>1</v>
       </c>
-      <c r="H33" s="2"/>
+      <c r="H33" s="2">
+        <v>1</v>
+      </c>
       <c r="I33" s="2">
         <v>1</v>
       </c>
-      <c r="J33" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>46256</v>
       </c>
@@ -1587,7 +1517,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="9">
         <v>46257</v>
       </c>
@@ -1604,7 +1534,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
         <v>46258</v>
       </c>
@@ -1623,17 +1553,14 @@
       <c r="F36" s="3">
         <v>1</v>
       </c>
+      <c r="H36" s="3">
+        <v>1</v>
+      </c>
       <c r="I36" s="3">
-        <v>1</v>
-      </c>
-      <c r="J36" s="3">
-        <v>2</v>
-      </c>
-      <c r="K36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="9">
         <v>46259</v>
       </c>
@@ -1649,11 +1576,11 @@
       <c r="E37" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>46260</v>
       </c>
@@ -1670,7 +1597,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="9">
         <v>46261</v>
       </c>
@@ -1686,20 +1613,17 @@
       <c r="E39" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F39" s="2"/>
+      <c r="F39" s="7"/>
       <c r="G39" s="2">
-        <v>2</v>
-      </c>
-      <c r="H39" s="2">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H39" s="2"/>
       <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="L39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="9">
         <v>46262</v>
       </c>
@@ -1715,25 +1639,21 @@
       <c r="E40" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="8">
         <v>1</v>
       </c>
       <c r="G40" s="2">
         <v>1</v>
       </c>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2">
-        <v>2</v>
-      </c>
-      <c r="J40" s="2"/>
-      <c r="L40">
-        <v>1</v>
-      </c>
-      <c r="M40">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H40" s="2">
+        <v>2</v>
+      </c>
+      <c r="I40" s="2"/>
+      <c r="J40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="9">
         <v>46263</v>
       </c>
@@ -1750,7 +1670,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="9">
         <v>46264</v>
       </c>
@@ -1767,7 +1687,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="9">
         <v>46265</v>
       </c>
@@ -1789,15 +1709,14 @@
       <c r="G43" s="2">
         <v>1</v>
       </c>
-      <c r="H43" s="2"/>
+      <c r="H43" s="2">
+        <v>1</v>
+      </c>
       <c r="I43" s="2">
         <v>1</v>
       </c>
-      <c r="J43" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="9">
         <v>46266</v>
       </c>
@@ -1816,17 +1735,14 @@
       <c r="F44" s="3">
         <v>1</v>
       </c>
+      <c r="H44" s="3">
+        <v>1</v>
+      </c>
       <c r="I44" s="3">
-        <v>1</v>
-      </c>
-      <c r="J44" s="3">
-        <v>2</v>
-      </c>
-      <c r="K44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="9">
         <v>46267</v>
       </c>
@@ -1842,11 +1758,11 @@
       <c r="E45" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L45">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="9">
         <v>46268</v>
       </c>
@@ -1862,20 +1778,17 @@
       <c r="E46" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F46" s="2"/>
+      <c r="F46" s="7"/>
       <c r="G46" s="2">
-        <v>2</v>
-      </c>
-      <c r="H46" s="2">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H46" s="2"/>
       <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="L46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="9">
         <v>46269</v>
       </c>
@@ -1892,7 +1805,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <v>46270</v>
       </c>
@@ -1909,7 +1822,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="9">
         <v>46271</v>
       </c>
@@ -1926,7 +1839,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="9">
         <v>46272</v>
       </c>
@@ -1942,25 +1855,21 @@
       <c r="E50" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="8">
         <v>1</v>
       </c>
       <c r="G50" s="2">
         <v>1</v>
       </c>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2">
-        <v>2</v>
-      </c>
-      <c r="J50" s="2"/>
-      <c r="L50">
-        <v>1</v>
-      </c>
-      <c r="M50">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H50" s="2">
+        <v>2</v>
+      </c>
+      <c r="I50" s="2"/>
+      <c r="J50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="9">
         <v>46273</v>
       </c>
@@ -1982,15 +1891,14 @@
       <c r="G51" s="2">
         <v>1</v>
       </c>
-      <c r="H51" s="2"/>
+      <c r="H51" s="2">
+        <v>1</v>
+      </c>
       <c r="I51" s="2">
         <v>1</v>
       </c>
-      <c r="J51" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <v>46274</v>
       </c>
@@ -2009,17 +1917,14 @@
       <c r="F52" s="3">
         <v>1</v>
       </c>
+      <c r="H52" s="3">
+        <v>1</v>
+      </c>
       <c r="I52" s="3">
-        <v>1</v>
-      </c>
-      <c r="J52" s="3">
-        <v>2</v>
-      </c>
-      <c r="K52">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="9">
         <v>46275</v>
       </c>
@@ -2035,11 +1940,11 @@
       <c r="E53" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L53">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <v>46276</v>
       </c>
@@ -2055,20 +1960,17 @@
       <c r="E54" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F54" s="2"/>
+      <c r="F54" s="7"/>
       <c r="G54" s="2">
-        <v>2</v>
-      </c>
-      <c r="H54" s="2">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H54" s="2"/>
       <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="L54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="9">
         <v>46277</v>
       </c>
@@ -2085,7 +1987,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <v>46278</v>
       </c>
@@ -2102,7 +2004,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="9">
         <v>46279</v>
       </c>
@@ -2119,7 +2021,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
         <v>46280</v>
       </c>
@@ -2135,25 +2037,21 @@
       <c r="E58" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="8">
         <v>1</v>
       </c>
       <c r="G58" s="2">
         <v>1</v>
       </c>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2">
-        <v>2</v>
-      </c>
-      <c r="J58" s="2"/>
-      <c r="L58">
-        <v>1</v>
-      </c>
-      <c r="M58">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H58" s="2">
+        <v>2</v>
+      </c>
+      <c r="I58" s="2"/>
+      <c r="J58">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="9">
         <v>46281</v>
       </c>
@@ -2175,15 +2073,14 @@
       <c r="G59" s="2">
         <v>1</v>
       </c>
-      <c r="H59" s="2"/>
+      <c r="H59" s="2">
+        <v>1</v>
+      </c>
       <c r="I59" s="2">
         <v>1</v>
       </c>
-      <c r="J59" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="9">
         <v>46282</v>
       </c>
@@ -2202,17 +2099,14 @@
       <c r="F60" s="3">
         <v>1</v>
       </c>
+      <c r="H60" s="3">
+        <v>1</v>
+      </c>
       <c r="I60" s="3">
-        <v>1</v>
-      </c>
-      <c r="J60" s="3">
-        <v>2</v>
-      </c>
-      <c r="K60">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="9">
         <v>46283</v>
       </c>
@@ -2228,11 +2122,11 @@
       <c r="E61" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L61">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="9">
         <v>46284</v>
       </c>
@@ -2249,7 +2143,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="9">
         <v>46285</v>
       </c>
@@ -2266,7 +2160,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="9">
         <v>46286</v>
       </c>
@@ -2282,20 +2176,17 @@
       <c r="E64" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F64" s="2"/>
+      <c r="F64" s="7"/>
       <c r="G64" s="2">
-        <v>2</v>
-      </c>
-      <c r="H64" s="2">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H64" s="2"/>
       <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
-      <c r="L64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="9">
         <v>46287</v>
       </c>
@@ -2311,25 +2202,21 @@
       <c r="E65" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="8">
         <v>1</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
       </c>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2">
-        <v>2</v>
-      </c>
-      <c r="J65" s="2"/>
-      <c r="L65">
-        <v>1</v>
-      </c>
-      <c r="M65">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H65" s="2">
+        <v>2</v>
+      </c>
+      <c r="I65" s="2"/>
+      <c r="J65">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>46288</v>
       </c>
@@ -2351,15 +2238,14 @@
       <c r="G66" s="2">
         <v>1</v>
       </c>
-      <c r="H66" s="2"/>
+      <c r="H66" s="2">
+        <v>1</v>
+      </c>
       <c r="I66" s="2">
         <v>1</v>
       </c>
-      <c r="J66" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="9">
         <v>46289</v>
       </c>
@@ -2378,17 +2264,14 @@
       <c r="F67" s="3">
         <v>1</v>
       </c>
+      <c r="H67" s="3">
+        <v>1</v>
+      </c>
       <c r="I67" s="3">
-        <v>1</v>
-      </c>
-      <c r="J67" s="3">
-        <v>2</v>
-      </c>
-      <c r="K67">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>46290</v>
       </c>
@@ -2404,11 +2287,11 @@
       <c r="E68" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L68">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="9">
         <v>46291</v>
       </c>
@@ -2425,7 +2308,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="9">
         <v>46292</v>
       </c>
@@ -2442,7 +2325,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="9">
         <v>46293</v>
       </c>
@@ -2458,20 +2341,17 @@
       <c r="E71" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F71" s="2"/>
+      <c r="F71" s="7"/>
       <c r="G71" s="2">
-        <v>2</v>
-      </c>
-      <c r="H71" s="2">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H71" s="2"/>
       <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-      <c r="L71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="9">
         <v>46294</v>
       </c>
@@ -2487,25 +2367,21 @@
       <c r="E72" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="8">
         <v>1</v>
       </c>
       <c r="G72" s="2">
         <v>1</v>
       </c>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2">
-        <v>2</v>
-      </c>
-      <c r="J72" s="2"/>
-      <c r="L72">
-        <v>1</v>
-      </c>
-      <c r="M72">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H72" s="2">
+        <v>2</v>
+      </c>
+      <c r="I72" s="2"/>
+      <c r="J72">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="9">
         <v>46295</v>
       </c>
@@ -2527,15 +2403,14 @@
       <c r="G73" s="2">
         <v>1</v>
       </c>
-      <c r="H73" s="2"/>
+      <c r="H73" s="2">
+        <v>1</v>
+      </c>
       <c r="I73" s="2">
         <v>1</v>
       </c>
-      <c r="J73" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="9">
         <v>46296</v>
       </c>
@@ -2554,17 +2429,14 @@
       <c r="F74" s="3">
         <v>1</v>
       </c>
+      <c r="H74" s="3">
+        <v>1</v>
+      </c>
       <c r="I74" s="3">
-        <v>1</v>
-      </c>
-      <c r="J74" s="3">
-        <v>2</v>
-      </c>
-      <c r="K74">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="9">
         <v>46297</v>
       </c>
@@ -2581,7 +2453,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="9">
         <v>46298</v>
       </c>
@@ -2598,7 +2470,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="9">
         <v>46299</v>
       </c>
@@ -2615,7 +2487,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="9">
         <v>46300</v>
       </c>
@@ -2631,11 +2503,11 @@
       <c r="E78" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L78">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="9">
         <v>46301</v>
       </c>
@@ -2651,23 +2523,17 @@
       <c r="E79" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F79" s="2"/>
+      <c r="F79" s="7"/>
       <c r="G79" s="2">
-        <v>2</v>
-      </c>
-      <c r="H79" s="2">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H79" s="2"/>
       <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-      <c r="L79">
-        <v>1</v>
-      </c>
-      <c r="M79">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="9">
         <v>46302</v>
       </c>
@@ -2683,22 +2549,21 @@
       <c r="E80" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80" s="8">
         <v>1</v>
       </c>
       <c r="G80" s="2">
         <v>1</v>
       </c>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2">
-        <v>2</v>
-      </c>
-      <c r="J80" s="2"/>
-      <c r="L80">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H80" s="2">
+        <v>2</v>
+      </c>
+      <c r="I80" s="2"/>
+      <c r="J80">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="9">
         <v>46303</v>
       </c>
@@ -2720,15 +2585,14 @@
       <c r="G81" s="2">
         <v>1</v>
       </c>
-      <c r="H81" s="2"/>
+      <c r="H81" s="2">
+        <v>1</v>
+      </c>
       <c r="I81" s="2">
         <v>1</v>
       </c>
-      <c r="J81" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="9">
         <v>46304</v>
       </c>
@@ -2747,17 +2611,14 @@
       <c r="F82" s="3">
         <v>1</v>
       </c>
+      <c r="H82" s="3">
+        <v>1</v>
+      </c>
       <c r="I82" s="3">
-        <v>1</v>
-      </c>
-      <c r="J82" s="3">
-        <v>2</v>
-      </c>
-      <c r="K82">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="9">
         <v>46305</v>
       </c>
@@ -2774,7 +2635,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="9">
         <v>46306</v>
       </c>
@@ -2791,7 +2652,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="9">
         <v>46307</v>
       </c>
@@ -2807,11 +2668,11 @@
       <c r="E85" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L85">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="9">
         <v>46308</v>
       </c>
@@ -2827,20 +2688,17 @@
       <c r="E86" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F86" s="2"/>
+      <c r="F86" s="7"/>
       <c r="G86" s="2">
-        <v>2</v>
-      </c>
-      <c r="H86" s="2">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H86" s="2"/>
       <c r="I86" s="2"/>
-      <c r="J86" s="2"/>
-      <c r="L86">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="9">
         <v>46309</v>
       </c>
@@ -2856,25 +2714,21 @@
       <c r="E87" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="8">
         <v>1</v>
       </c>
       <c r="G87" s="2">
         <v>1</v>
       </c>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2">
-        <v>2</v>
-      </c>
-      <c r="J87" s="2"/>
-      <c r="L87">
-        <v>1</v>
-      </c>
-      <c r="M87">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H87" s="2">
+        <v>2</v>
+      </c>
+      <c r="I87" s="2"/>
+      <c r="J87">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="9">
         <v>46310</v>
       </c>
@@ -2896,15 +2750,14 @@
       <c r="G88" s="2">
         <v>1</v>
       </c>
-      <c r="H88" s="2"/>
+      <c r="H88" s="2">
+        <v>1</v>
+      </c>
       <c r="I88" s="2">
         <v>1</v>
       </c>
-      <c r="J88" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="9">
         <v>46311</v>
       </c>
@@ -2923,17 +2776,14 @@
       <c r="F89" s="3">
         <v>1</v>
       </c>
+      <c r="H89" s="3">
+        <v>1</v>
+      </c>
       <c r="I89" s="3">
-        <v>1</v>
-      </c>
-      <c r="J89" s="3">
-        <v>2</v>
-      </c>
-      <c r="K89">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="9">
         <v>46312</v>
       </c>
@@ -2950,7 +2800,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="9">
         <v>46313</v>
       </c>
@@ -2967,7 +2817,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="9">
         <v>46314</v>
       </c>
@@ -2984,7 +2834,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="9">
         <v>46315</v>
       </c>
@@ -3001,7 +2851,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="9">
         <v>46316</v>
       </c>
@@ -3017,11 +2867,11 @@
       <c r="E94" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L94">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="9">
         <v>46317</v>
       </c>
@@ -3037,20 +2887,17 @@
       <c r="E95" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F95" s="2"/>
+      <c r="F95" s="7"/>
       <c r="G95" s="2">
-        <v>2</v>
-      </c>
-      <c r="H95" s="2">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H95" s="2"/>
       <c r="I95" s="2"/>
-      <c r="J95" s="2"/>
-      <c r="L95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="9">
         <v>46318</v>
       </c>
@@ -3066,25 +2913,21 @@
       <c r="E96" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="8">
         <v>1</v>
       </c>
       <c r="G96" s="2">
         <v>1</v>
       </c>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2">
-        <v>2</v>
-      </c>
-      <c r="J96" s="2"/>
-      <c r="L96">
-        <v>1</v>
-      </c>
-      <c r="M96">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H96" s="2">
+        <v>2</v>
+      </c>
+      <c r="I96" s="2"/>
+      <c r="J96">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="9">
         <v>46319</v>
       </c>
@@ -3101,7 +2944,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="9">
         <v>46320</v>
       </c>
@@ -3118,7 +2961,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="9">
         <v>46321</v>
       </c>
@@ -3140,15 +2983,14 @@
       <c r="G99" s="2">
         <v>1</v>
       </c>
-      <c r="H99" s="2"/>
+      <c r="H99" s="2">
+        <v>1</v>
+      </c>
       <c r="I99" s="2">
         <v>1</v>
       </c>
-      <c r="J99" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="9">
         <v>46322</v>
       </c>
@@ -3167,17 +3009,14 @@
       <c r="F100" s="3">
         <v>1</v>
       </c>
+      <c r="H100" s="3">
+        <v>1</v>
+      </c>
       <c r="I100" s="3">
-        <v>1</v>
-      </c>
-      <c r="J100" s="3">
-        <v>2</v>
-      </c>
-      <c r="K100">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="9">
         <v>46323</v>
       </c>
@@ -3193,11 +3032,11 @@
       <c r="E101" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L101">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="9">
         <v>46324</v>
       </c>
@@ -3213,20 +3052,17 @@
       <c r="E102" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F102" s="2"/>
+      <c r="F102" s="7"/>
       <c r="G102" s="2">
-        <v>2</v>
-      </c>
-      <c r="H102" s="2">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H102" s="2"/>
       <c r="I102" s="2"/>
-      <c r="J102" s="2"/>
-      <c r="L102">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="9">
         <v>46325</v>
       </c>
@@ -3242,25 +3078,21 @@
       <c r="E103" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F103" s="2">
+      <c r="F103" s="8">
         <v>1</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
       </c>
-      <c r="H103" s="2"/>
-      <c r="I103" s="2">
-        <v>2</v>
-      </c>
-      <c r="J103" s="2"/>
-      <c r="L103">
-        <v>1</v>
-      </c>
-      <c r="M103">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H103" s="2">
+        <v>2</v>
+      </c>
+      <c r="I103" s="2"/>
+      <c r="J103">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="9">
         <v>46326</v>
       </c>
@@ -3277,7 +3109,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="9">
         <v>46327</v>
       </c>
@@ -3294,7 +3126,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="9">
         <v>46328</v>
       </c>
@@ -3316,15 +3148,14 @@
       <c r="G106" s="2">
         <v>1</v>
       </c>
-      <c r="H106" s="2"/>
+      <c r="H106" s="2">
+        <v>1</v>
+      </c>
       <c r="I106" s="2">
         <v>1</v>
       </c>
-      <c r="J106" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="9">
         <v>46329</v>
       </c>
@@ -3343,17 +3174,14 @@
       <c r="F107" s="3">
         <v>1</v>
       </c>
+      <c r="H107" s="3">
+        <v>1</v>
+      </c>
       <c r="I107" s="3">
-        <v>1</v>
-      </c>
-      <c r="J107" s="3">
-        <v>2</v>
-      </c>
-      <c r="K107">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="9">
         <v>46330</v>
       </c>
@@ -3369,11 +3197,11 @@
       <c r="E108" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L108">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="9">
         <v>46331</v>
       </c>
@@ -3389,20 +3217,17 @@
       <c r="E109" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F109" s="2"/>
+      <c r="F109" s="7"/>
       <c r="G109" s="2">
-        <v>2</v>
-      </c>
-      <c r="H109" s="2">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H109" s="2"/>
       <c r="I109" s="2"/>
-      <c r="J109" s="2"/>
-      <c r="L109">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="9">
         <v>46332</v>
       </c>
@@ -3418,25 +3243,21 @@
       <c r="E110" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F110" s="2">
+      <c r="F110" s="8">
         <v>1</v>
       </c>
       <c r="G110" s="2">
         <v>1</v>
       </c>
-      <c r="H110" s="2"/>
-      <c r="I110" s="2">
-        <v>2</v>
-      </c>
-      <c r="J110" s="2"/>
-      <c r="L110">
-        <v>1</v>
-      </c>
-      <c r="M110">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H110" s="2">
+        <v>2</v>
+      </c>
+      <c r="I110" s="2"/>
+      <c r="J110">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="9">
         <v>46333</v>
       </c>
@@ -3453,7 +3274,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="9">
         <v>46334</v>
       </c>
@@ -3470,7 +3291,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="9">
         <v>46335</v>
       </c>
@@ -3492,15 +3313,14 @@
       <c r="G113" s="2">
         <v>1</v>
       </c>
-      <c r="H113" s="2"/>
+      <c r="H113" s="2">
+        <v>1</v>
+      </c>
       <c r="I113" s="2">
         <v>1</v>
       </c>
-      <c r="J113" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="9">
         <v>46336</v>
       </c>
@@ -3519,17 +3339,14 @@
       <c r="F114" s="3">
         <v>1</v>
       </c>
+      <c r="H114" s="3">
+        <v>1</v>
+      </c>
       <c r="I114" s="3">
-        <v>1</v>
-      </c>
-      <c r="J114" s="3">
-        <v>2</v>
-      </c>
-      <c r="K114">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="9">
         <v>46337</v>
       </c>
@@ -3545,11 +3362,11 @@
       <c r="E115" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L115">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="9">
         <v>46338</v>
       </c>
@@ -3565,20 +3382,17 @@
       <c r="E116" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F116" s="2"/>
+      <c r="F116" s="7"/>
       <c r="G116" s="2">
-        <v>2</v>
-      </c>
-      <c r="H116" s="2">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H116" s="2"/>
       <c r="I116" s="2"/>
-      <c r="J116" s="2"/>
-      <c r="L116">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="9">
         <v>46339</v>
       </c>
@@ -3594,25 +3408,21 @@
       <c r="E117" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F117" s="2">
+      <c r="F117" s="8">
         <v>1</v>
       </c>
       <c r="G117" s="2">
         <v>1</v>
       </c>
-      <c r="H117" s="2"/>
-      <c r="I117" s="2">
-        <v>2</v>
-      </c>
-      <c r="J117" s="2"/>
-      <c r="L117">
-        <v>1</v>
-      </c>
-      <c r="M117">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H117" s="2">
+        <v>2</v>
+      </c>
+      <c r="I117" s="2"/>
+      <c r="J117">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="9">
         <v>46340</v>
       </c>
@@ -3629,7 +3439,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="9">
         <v>46341</v>
       </c>
@@ -3646,7 +3456,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="9">
         <v>46342</v>
       </c>
@@ -3668,15 +3478,14 @@
       <c r="G120" s="2">
         <v>1</v>
       </c>
-      <c r="H120" s="2"/>
+      <c r="H120" s="2">
+        <v>1</v>
+      </c>
       <c r="I120" s="2">
         <v>1</v>
       </c>
-      <c r="J120" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="9">
         <v>46343</v>
       </c>
@@ -3695,17 +3504,14 @@
       <c r="F121" s="3">
         <v>1</v>
       </c>
+      <c r="H121" s="3">
+        <v>1</v>
+      </c>
       <c r="I121" s="3">
-        <v>1</v>
-      </c>
-      <c r="J121" s="3">
-        <v>2</v>
-      </c>
-      <c r="K121">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="9">
         <v>46344</v>
       </c>
@@ -3721,11 +3527,11 @@
       <c r="E122" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L122">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="9">
         <v>46345</v>
       </c>
@@ -3741,20 +3547,17 @@
       <c r="E123" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F123" s="2"/>
+      <c r="F123" s="7"/>
       <c r="G123" s="2">
-        <v>2</v>
-      </c>
-      <c r="H123" s="2">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H123" s="2"/>
       <c r="I123" s="2"/>
-      <c r="J123" s="2"/>
-      <c r="L123">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="9">
         <v>46346</v>
       </c>
@@ -3770,25 +3573,21 @@
       <c r="E124" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F124" s="2">
+      <c r="F124" s="8">
         <v>1</v>
       </c>
       <c r="G124" s="2">
         <v>1</v>
       </c>
-      <c r="H124" s="2"/>
-      <c r="I124" s="2">
-        <v>2</v>
-      </c>
-      <c r="J124" s="2"/>
-      <c r="L124">
-        <v>1</v>
-      </c>
-      <c r="M124">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H124" s="2">
+        <v>2</v>
+      </c>
+      <c r="I124" s="2"/>
+      <c r="J124">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="9">
         <v>46347</v>
       </c>
@@ -3805,7 +3604,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="9">
         <v>46348</v>
       </c>
@@ -3822,7 +3621,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="9">
         <v>46349</v>
       </c>
@@ -3844,15 +3643,14 @@
       <c r="G127" s="2">
         <v>1</v>
       </c>
-      <c r="H127" s="2"/>
+      <c r="H127" s="2">
+        <v>1</v>
+      </c>
       <c r="I127" s="2">
         <v>1</v>
       </c>
-      <c r="J127" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="9">
         <v>46350</v>
       </c>
@@ -3871,17 +3669,14 @@
       <c r="F128" s="3">
         <v>1</v>
       </c>
+      <c r="H128" s="3">
+        <v>1</v>
+      </c>
       <c r="I128" s="3">
-        <v>1</v>
-      </c>
-      <c r="J128" s="3">
-        <v>2</v>
-      </c>
-      <c r="K128">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="9">
         <v>46351</v>
       </c>
@@ -3897,11 +3692,11 @@
       <c r="E129" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L129">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J129">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="9">
         <v>46352</v>
       </c>
@@ -3917,20 +3712,17 @@
       <c r="E130" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F130" s="2"/>
+      <c r="F130" s="7"/>
       <c r="G130" s="2">
-        <v>2</v>
-      </c>
-      <c r="H130" s="2">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H130" s="2"/>
       <c r="I130" s="2"/>
-      <c r="J130" s="2"/>
-      <c r="L130">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="9">
         <v>46353</v>
       </c>
@@ -3946,25 +3738,21 @@
       <c r="E131" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F131" s="2">
+      <c r="F131" s="8">
         <v>1</v>
       </c>
       <c r="G131" s="2">
         <v>1</v>
       </c>
-      <c r="H131" s="2"/>
-      <c r="I131" s="2">
-        <v>2</v>
-      </c>
-      <c r="J131" s="2"/>
-      <c r="L131">
-        <v>1</v>
-      </c>
-      <c r="M131">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H131" s="2">
+        <v>2</v>
+      </c>
+      <c r="I131" s="2"/>
+      <c r="J131">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="9">
         <v>46354</v>
       </c>
@@ -3981,7 +3769,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="9">
         <v>46355</v>
       </c>
@@ -3998,7 +3786,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="9">
         <v>46356</v>
       </c>
@@ -4020,15 +3808,14 @@
       <c r="G134" s="2">
         <v>1</v>
       </c>
-      <c r="H134" s="2"/>
+      <c r="H134" s="2">
+        <v>1</v>
+      </c>
       <c r="I134" s="2">
         <v>1</v>
       </c>
-      <c r="J134" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="9">
         <v>46357</v>
       </c>
@@ -4047,17 +3834,14 @@
       <c r="F135" s="3">
         <v>1</v>
       </c>
+      <c r="H135" s="3">
+        <v>1</v>
+      </c>
       <c r="I135" s="3">
-        <v>1</v>
-      </c>
-      <c r="J135" s="3">
-        <v>2</v>
-      </c>
-      <c r="K135">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="9">
         <v>46358</v>
       </c>
@@ -4073,11 +3857,11 @@
       <c r="E136" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L136">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J136">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="9">
         <v>46359</v>
       </c>
@@ -4093,20 +3877,17 @@
       <c r="E137" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F137" s="2"/>
+      <c r="F137" s="7"/>
       <c r="G137" s="2">
-        <v>2</v>
-      </c>
-      <c r="H137" s="2">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H137" s="2"/>
       <c r="I137" s="2"/>
-      <c r="J137" s="2"/>
-      <c r="L137">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="9">
         <v>46360</v>
       </c>
@@ -4122,25 +3903,21 @@
       <c r="E138" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F138" s="2">
+      <c r="F138" s="8">
         <v>1</v>
       </c>
       <c r="G138" s="2">
         <v>1</v>
       </c>
-      <c r="H138" s="2"/>
-      <c r="I138" s="2">
-        <v>2</v>
-      </c>
-      <c r="J138" s="2"/>
-      <c r="L138">
-        <v>1</v>
-      </c>
-      <c r="M138">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H138" s="2">
+        <v>2</v>
+      </c>
+      <c r="I138" s="2"/>
+      <c r="J138">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="9">
         <v>46361</v>
       </c>
@@ -4157,7 +3934,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="9">
         <v>46362</v>
       </c>
@@ -4174,7 +3951,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="9">
         <v>46363</v>
       </c>
@@ -4196,11 +3973,10 @@
       <c r="G141" s="2">
         <v>1</v>
       </c>
-      <c r="H141" s="2"/>
+      <c r="H141" s="2">
+        <v>1</v>
+      </c>
       <c r="I141" s="2">
-        <v>1</v>
-      </c>
-      <c r="J141" s="2">
         <v>1</v>
       </c>
     </row>

--- a/main/academic_time_table.xlsx
+++ b/main/academic_time_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ronak_8q45q08\Desktop\Ronak\srm attendance calculator\calc_attendence\main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74EEE1E8-CA55-4E33-8D01-6FB3B324062B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C894B3-F019-4AB3-BD4C-79630E40B2E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{A757884B-7843-4405-99AB-51A9CEB2882C}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="43">
   <si>
     <t>Holiday</t>
   </si>
@@ -151,12 +151,6 @@
   </si>
   <si>
     <t>Wk 17</t>
-  </si>
-  <si>
-    <t>Wk 18</t>
-  </si>
-  <si>
-    <t>Wk 19</t>
   </si>
   <si>
     <t>Status</t>
@@ -705,19 +699,19 @@
         <v>6</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>5</v>
@@ -3588,397 +3582,151 @@
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A125" s="9">
-        <v>46347</v>
-      </c>
-      <c r="B125" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C125" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D125" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E125" s="16" t="s">
-        <v>17</v>
-      </c>
+      <c r="A125" s="9"/>
+      <c r="B125" s="10"/>
+      <c r="C125" s="15"/>
+      <c r="D125" s="12"/>
+      <c r="E125" s="16"/>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A126" s="9">
-        <v>46348</v>
-      </c>
-      <c r="B126" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C126" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D126" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E126" s="16" t="s">
-        <v>17</v>
-      </c>
+      <c r="A126" s="9"/>
+      <c r="B126" s="10"/>
+      <c r="C126" s="15"/>
+      <c r="D126" s="12"/>
+      <c r="E126" s="16"/>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A127" s="9">
-        <v>46349</v>
-      </c>
-      <c r="B127" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C127" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D127" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E127" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="F127" s="2">
-        <v>2</v>
-      </c>
-      <c r="G127" s="2">
-        <v>1</v>
-      </c>
-      <c r="H127" s="2">
-        <v>1</v>
-      </c>
-      <c r="I127" s="2">
-        <v>1</v>
-      </c>
+      <c r="A127" s="9"/>
+      <c r="B127" s="10"/>
+      <c r="C127" s="11"/>
+      <c r="D127" s="12"/>
+      <c r="E127" s="13"/>
+      <c r="F127" s="2"/>
+      <c r="G127" s="2"/>
+      <c r="H127" s="2"/>
+      <c r="I127" s="2"/>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A128" s="9">
-        <v>46350</v>
-      </c>
-      <c r="B128" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C128" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D128" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E128" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F128" s="3">
-        <v>1</v>
-      </c>
-      <c r="H128" s="3">
-        <v>1</v>
-      </c>
-      <c r="I128" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A129" s="9">
-        <v>46351</v>
-      </c>
-      <c r="B129" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C129" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D129" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E129" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J129">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A130" s="9">
-        <v>46352</v>
-      </c>
-      <c r="B130" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C130" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D130" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E130" s="13" t="s">
-        <v>18</v>
-      </c>
+      <c r="A128" s="9"/>
+      <c r="B128" s="10"/>
+      <c r="C128" s="11"/>
+      <c r="D128" s="12"/>
+      <c r="E128" s="13"/>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A129" s="9"/>
+      <c r="B129" s="10"/>
+      <c r="C129" s="11"/>
+      <c r="D129" s="12"/>
+      <c r="E129" s="13"/>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A130" s="9"/>
+      <c r="B130" s="10"/>
+      <c r="C130" s="11"/>
+      <c r="D130" s="12"/>
+      <c r="E130" s="13"/>
       <c r="F130" s="7"/>
-      <c r="G130" s="2">
-        <v>4</v>
-      </c>
+      <c r="G130" s="2"/>
       <c r="H130" s="2"/>
       <c r="I130" s="2"/>
-      <c r="J130">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A131" s="9">
-        <v>46353</v>
-      </c>
-      <c r="B131" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C131" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D131" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E131" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F131" s="8">
-        <v>1</v>
-      </c>
-      <c r="G131" s="2">
-        <v>1</v>
-      </c>
-      <c r="H131" s="2">
-        <v>2</v>
-      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A131" s="9"/>
+      <c r="B131" s="10"/>
+      <c r="C131" s="11"/>
+      <c r="D131" s="12"/>
+      <c r="E131" s="13"/>
+      <c r="F131" s="8"/>
+      <c r="G131" s="2"/>
+      <c r="H131" s="2"/>
       <c r="I131" s="2"/>
-      <c r="J131">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A132" s="9">
-        <v>46354</v>
-      </c>
-      <c r="B132" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C132" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D132" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E132" s="16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A133" s="9">
-        <v>46355</v>
-      </c>
-      <c r="B133" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C133" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D133" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E133" s="16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A134" s="9">
-        <v>46356</v>
-      </c>
-      <c r="B134" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C134" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D134" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E134" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="F134" s="2">
-        <v>2</v>
-      </c>
-      <c r="G134" s="2">
-        <v>1</v>
-      </c>
-      <c r="H134" s="2">
-        <v>1</v>
-      </c>
-      <c r="I134" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A135" s="9">
-        <v>46357</v>
-      </c>
-      <c r="B135" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C135" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D135" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E135" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F135" s="3">
-        <v>1</v>
-      </c>
-      <c r="H135" s="3">
-        <v>1</v>
-      </c>
-      <c r="I135" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A136" s="9">
-        <v>46358</v>
-      </c>
-      <c r="B136" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C136" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D136" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E136" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J136">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A137" s="9">
-        <v>46359</v>
-      </c>
-      <c r="B137" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C137" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D137" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E137" s="13" t="s">
-        <v>18</v>
-      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A132" s="9"/>
+      <c r="B132" s="10"/>
+      <c r="C132" s="15"/>
+      <c r="D132" s="12"/>
+      <c r="E132" s="16"/>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A133" s="9"/>
+      <c r="B133" s="10"/>
+      <c r="C133" s="15"/>
+      <c r="D133" s="12"/>
+      <c r="E133" s="16"/>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A134" s="9"/>
+      <c r="B134" s="10"/>
+      <c r="C134" s="11"/>
+      <c r="D134" s="12"/>
+      <c r="E134" s="13"/>
+      <c r="F134" s="2"/>
+      <c r="G134" s="2"/>
+      <c r="H134" s="2"/>
+      <c r="I134" s="2"/>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A135" s="9"/>
+      <c r="B135" s="10"/>
+      <c r="C135" s="11"/>
+      <c r="D135" s="12"/>
+      <c r="E135" s="13"/>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A136" s="9"/>
+      <c r="B136" s="10"/>
+      <c r="C136" s="11"/>
+      <c r="D136" s="12"/>
+      <c r="E136" s="13"/>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A137" s="9"/>
+      <c r="B137" s="10"/>
+      <c r="C137" s="11"/>
+      <c r="D137" s="12"/>
+      <c r="E137" s="13"/>
       <c r="F137" s="7"/>
-      <c r="G137" s="2">
-        <v>4</v>
-      </c>
+      <c r="G137" s="2"/>
       <c r="H137" s="2"/>
       <c r="I137" s="2"/>
-      <c r="J137">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A138" s="9">
-        <v>46360</v>
-      </c>
-      <c r="B138" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C138" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D138" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E138" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F138" s="8">
-        <v>1</v>
-      </c>
-      <c r="G138" s="2">
-        <v>1</v>
-      </c>
-      <c r="H138" s="2">
-        <v>2</v>
-      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A138" s="9"/>
+      <c r="B138" s="10"/>
+      <c r="C138" s="11"/>
+      <c r="D138" s="12"/>
+      <c r="E138" s="13"/>
+      <c r="F138" s="8"/>
+      <c r="G138" s="2"/>
+      <c r="H138" s="2"/>
       <c r="I138" s="2"/>
-      <c r="J138">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A139" s="9">
-        <v>46361</v>
-      </c>
-      <c r="B139" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C139" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D139" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E139" s="16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A140" s="9">
-        <v>46362</v>
-      </c>
-      <c r="B140" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C140" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D140" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E140" s="16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A141" s="9">
-        <v>46363</v>
-      </c>
-      <c r="B141" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C141" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D141" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E141" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="F141" s="2">
-        <v>2</v>
-      </c>
-      <c r="G141" s="2">
-        <v>1</v>
-      </c>
-      <c r="H141" s="2">
-        <v>1</v>
-      </c>
-      <c r="I141" s="2">
-        <v>1</v>
-      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A139" s="9"/>
+      <c r="B139" s="10"/>
+      <c r="C139" s="15"/>
+      <c r="D139" s="12"/>
+      <c r="E139" s="16"/>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A140" s="9"/>
+      <c r="B140" s="10"/>
+      <c r="C140" s="15"/>
+      <c r="D140" s="12"/>
+      <c r="E140" s="16"/>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A141" s="9"/>
+      <c r="B141" s="10"/>
+      <c r="C141" s="11"/>
+      <c r="D141" s="12"/>
+      <c r="E141" s="13"/>
+      <c r="F141" s="2"/>
+      <c r="G141" s="2"/>
+      <c r="H141" s="2"/>
+      <c r="I141" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
